--- a/feature-cb-ibd-ig/StructureDefinition-SIMFasering.xlsx
+++ b/feature-cb-ibd-ig/StructureDefinition-SIMFasering.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2037" uniqueCount="267">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T14:27:57+00:00</t>
+    <t>2026-10-26T15:58:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -584,6 +584,34 @@
     <t>Identificatienummer_value</t>
   </si>
   <si>
+    <t>SIMFasering.Patient.Geslacht</t>
+  </si>
+  <si>
+    <t>Administratief geslacht van de patiënt</t>
+  </si>
+  <si>
+    <t>http://decor.nictiz.nl/fhir/ValueSet/2.16.840.1.113883.2.4.3.11.60.40.2.17.1.8--20200901000000</t>
+  </si>
+  <si>
+    <t>SIMPatient.Geslacht</t>
+  </si>
+  <si>
+    <t>SIMFasering.Patient.Land</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Land waar het adres zich bevindt</t>
+  </si>
+  <si>
+    <t>http://decor.nictiz.nl/fhir/ValueSet/2.16.840.1.113883.2.4.3.11.60.40.2.20.5.2--20200901000000</t>
+  </si>
+  <si>
+    <t>SIMPatient.Land</t>
+  </si>
+  <si>
     <t>SIMFasering.Patient.Geboortedatum</t>
   </si>
   <si>
@@ -597,84 +625,194 @@
     <t>SIMPatient.Geboortedatum</t>
   </si>
   <si>
-    <t>SIMFasering.FaseringType</t>
-  </si>
-  <si>
-    <t>Type procesfasering</t>
-  </si>
-  <si>
-    <t>Encounter.type</t>
-  </si>
-  <si>
-    <t>SIMFasering.FaseringType.id</t>
-  </si>
-  <si>
-    <t>SIMFasering.FaseringType.extension</t>
-  </si>
-  <si>
-    <t>SIMFasering.FaseringType.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>SIMFasering.FaseringType.coding.system</t>
-  </si>
-  <si>
-    <t>FaseringCodeSysteem</t>
-  </si>
-  <si>
-    <t>SIMFasering.FaseringType.coding.code</t>
-  </si>
-  <si>
-    <t>FaseringCode</t>
-  </si>
-  <si>
-    <t>SIMFasering.FaseringType.coding.display</t>
-  </si>
-  <si>
-    <t>FaseringOmschrijving</t>
-  </si>
-  <si>
-    <t>SIMFasering.FaseringType.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>SIMFasering.BeginDatumTijd</t>
+    <t>SIMFasering.Patient.DatumOverlijden</t>
   </si>
   <si>
     <t xml:space="preserve">dateTime
 </t>
+  </si>
+  <si>
+    <t>Datum waarop de patiënt is overleden</t>
+  </si>
+  <si>
+    <t>SIMPatient.DatumOverlijden</t>
+  </si>
+  <si>
+    <t>SIMFasering.Patient.DatumCheckStatusOverlijden</t>
+  </si>
+  <si>
+    <t>Datum waarop de overlijdensstatus is gecontroleerd</t>
+  </si>
+  <si>
+    <t>SIMPatient.DatumCheckStatusOverlijden</t>
+  </si>
+  <si>
+    <t>SIMFasering.Patient.GerelateerdePersoon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Gerelateerde persoon</t>
+  </si>
+  <si>
+    <t>SIMPatient.GerelateerdePersoon</t>
+  </si>
+  <si>
+    <t>SIMFasering.Patient.GerelateerdePersoon.id</t>
+  </si>
+  <si>
+    <t>SIMFasering.Patient.GerelateerdePersoon.extension</t>
+  </si>
+  <si>
+    <t>SIMFasering.Patient.GerelateerdePersoon.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>SIMFasering.Patient.GerelateerdePersoon.Identificatienummer</t>
+  </si>
+  <si>
+    <t>Identificatienummer van de gerelateerde persoon</t>
+  </si>
+  <si>
+    <t>SIMPatient.GerelateerdePersoon.Identificatienummer</t>
+  </si>
+  <si>
+    <t>SIMFasering.Patient.GerelateerdePersoon.Relatie</t>
+  </si>
+  <si>
+    <t>Relatie tot de patiënt</t>
+  </si>
+  <si>
+    <t>http://decor.nictiz.nl/fhir/ValueSet/2.16.840.1.113883.2.4.3.11.60.40.2.3.1.1--20200901000000</t>
+  </si>
+  <si>
+    <t>SIMPatient.GerelateerdePersoon.Relatie</t>
+  </si>
+  <si>
+    <t>SIMFasering.Patient.Naam</t>
+  </si>
+  <si>
+    <t>Naam van de patiënt</t>
+  </si>
+  <si>
+    <t>SIMPatient.Naam</t>
+  </si>
+  <si>
+    <t>SIMFasering.Patient.Naam.id</t>
+  </si>
+  <si>
+    <t>SIMFasering.Patient.Naam.extension</t>
+  </si>
+  <si>
+    <t>SIMFasering.Patient.Naam.modifierExtension</t>
+  </si>
+  <si>
+    <t>SIMFasering.Patient.Naam.Initialen</t>
+  </si>
+  <si>
+    <t>Initialen van de patiënt</t>
+  </si>
+  <si>
+    <t>SIMPatient.Naam.Initialen</t>
+  </si>
+  <si>
+    <t>SIMFasering.Patient.Naam.Achternaam</t>
+  </si>
+  <si>
+    <t>Achternaam van de patiënt</t>
+  </si>
+  <si>
+    <t>SIMPatient.Naam.Achternaam</t>
+  </si>
+  <si>
+    <t>SIMFasering.FaseringType</t>
+  </si>
+  <si>
+    <t>Type procesfasering</t>
+  </si>
+  <si>
+    <t>Encounter.type</t>
+  </si>
+  <si>
+    <t>SIMFasering.FaseringType.id</t>
+  </si>
+  <si>
+    <t>SIMFasering.FaseringType.extension</t>
+  </si>
+  <si>
+    <t>SIMFasering.FaseringType.coding</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>SIMFasering.FaseringType.coding.system</t>
+  </si>
+  <si>
+    <t>FaseringCodeSysteem</t>
+  </si>
+  <si>
+    <t>SIMFasering.FaseringType.coding.code</t>
+  </si>
+  <si>
+    <t>FaseringCode</t>
+  </si>
+  <si>
+    <t>SIMFasering.FaseringType.coding.display</t>
+  </si>
+  <si>
+    <t>FaseringOmschrijving</t>
+  </si>
+  <si>
+    <t>SIMFasering.FaseringType.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>SIMFasering.BeginDatumTijd</t>
   </si>
   <si>
     <t>Datum en tijd waarop de fasering begint</t>
@@ -997,13 +1135,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL44"/>
+  <dimension ref="A1:AL60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.1484375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="39.1484375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="50.125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="50.125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
@@ -1014,7 +1152,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="196.6875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -1025,13 +1163,13 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="38.1484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="77.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="39.1484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="42.89453125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -4598,7 +4736,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>80</v>
@@ -4613,13 +4751,13 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="L34" t="s" s="2">
-        <v>187</v>
-      </c>
       <c r="M34" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4646,13 +4784,11 @@
         <v>74</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>74</v>
+        <v>187</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>74</v>
@@ -4673,7 +4809,7 @@
         <v>188</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>80</v>
@@ -4704,7 +4840,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>80</v>
@@ -4719,13 +4855,13 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>113</v>
+        <v>190</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4752,13 +4888,11 @@
         <v>74</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>74</v>
+        <v>192</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>74</v>
@@ -4776,10 +4910,10 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>80</v>
@@ -4788,21 +4922,21 @@
         <v>74</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>191</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4810,7 +4944,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>80</v>
@@ -4825,13 +4959,13 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>86</v>
+        <v>195</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>87</v>
+        <v>196</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>88</v>
+        <v>196</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4882,10 +5016,10 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>89</v>
+        <v>197</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>80</v>
@@ -4905,21 +5039,21 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>74</v>
@@ -4931,17 +5065,15 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>92</v>
+        <v>199</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>93</v>
+        <v>200</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>95</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>74</v>
@@ -4978,31 +5110,31 @@
         <v>74</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>99</v>
+        <v>201</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>74</v>
@@ -5013,10 +5145,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5027,7 +5159,7 @@
         <v>75</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>74</v>
@@ -5036,23 +5168,19 @@
         <v>74</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>74</v>
       </c>
@@ -5100,19 +5228,19 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>74</v>
@@ -5123,10 +5251,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5136,7 +5264,9 @@
       <c r="F39" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G39" s="2"/>
+      <c r="G39" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="H39" t="s" s="2">
         <v>74</v>
       </c>
@@ -5147,10 +5277,14 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5200,20 +5334,22 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH39" s="2"/>
+      <c r="AH39" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="AI39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>202</v>
+        <v>74</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>74</v>
@@ -5221,10 +5357,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5234,7 +5370,9 @@
       <c r="F40" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G40" s="2"/>
+      <c r="G40" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="H40" t="s" s="2">
         <v>74</v>
       </c>
@@ -5245,10 +5383,14 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="L40" s="2"/>
-      <c r="M40" s="2"/>
+        <v>86</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>88</v>
+      </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5298,12 +5440,14 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>203</v>
+        <v>89</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH40" s="2"/>
+      <c r="AH40" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AI40" t="s" s="2">
         <v>74</v>
       </c>
@@ -5311,7 +5455,7 @@
         <v>74</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>204</v>
+        <v>74</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>74</v>
@@ -5319,20 +5463,22 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="G41" s="2"/>
+      <c r="G41" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="H41" t="s" s="2">
         <v>74</v>
       </c>
@@ -5343,11 +5489,17 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="L41" s="2"/>
-      <c r="M41" s="2"/>
-      <c r="N41" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>95</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>74</v>
@@ -5384,32 +5536,34 @@
         <v>74</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>205</v>
+        <v>99</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AH41" s="2"/>
+      <c r="AH41" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="AI41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>206</v>
+        <v>74</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>74</v>
@@ -5417,45 +5571,45 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>74</v>
+        <v>212</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="J42" t="s" s="2">
         <v>102</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>210</v>
+        <v>95</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>74</v>
@@ -5504,19 +5658,19 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>74</v>
@@ -5527,10 +5681,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5538,7 +5692,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>80</v>
@@ -5553,13 +5707,13 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>214</v>
+        <v>81</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5610,10 +5764,10 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>80</v>
@@ -5625,18 +5779,18 @@
         <v>74</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>216</v>
+        <v>74</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>217</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5644,7 +5798,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>80</v>
@@ -5659,13 +5813,13 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>214</v>
+        <v>113</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5692,13 +5846,11 @@
         <v>74</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>74</v>
+        <v>222</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>74</v>
@@ -5716,10 +5868,10 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>80</v>
@@ -5731,10 +5883,1698 @@
         <v>74</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>220</v>
+        <v>74</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>221</v>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="P48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="P54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G55" s="2"/>
+      <c r="H55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L55" s="2"/>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH55" s="2"/>
+      <c r="AI55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G56" s="2"/>
+      <c r="H56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH56" s="2"/>
+      <c r="AI56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G57" s="2"/>
+      <c r="H57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="L57" s="2"/>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH57" s="2"/>
+      <c r="AI57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>266</v>
       </c>
     </row>
   </sheetData>
